--- a/5.26.26 Climate Tracker v2.xlsx
+++ b/5.26.26 Climate Tracker v2.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="dddd, d. mmmm yyyy"/>
+    <numFmt numFmtId="165" formatCode="dddd, d. mmmm yyyy"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -265,7 +264,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -405,10 +404,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1637,7 +1639,7 @@
           <t>To direct the Secretary of Energy to report to Congress on the use of electric energy and water by certain data centers, and for other purposes.</t>
         </is>
       </c>
-      <c r="C6" s="49" t="n">
+      <c r="C6" s="51" t="n">
         <v>46164</v>
       </c>
       <c r="D6" s="48" t="inlineStr">
@@ -1674,7 +1676,7 @@
           <t>Energy and Water Development and Related Agencies Appropriations Act, 2027</t>
         </is>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="51" t="n">
         <v>46164</v>
       </c>
       <c r="D7" s="48" t="inlineStr">
@@ -1711,7 +1713,7 @@
           <t>Expressing support for the designation of the month of May 2026 as "Progressive Supranuclear Palsy and Corticobasal Degeneration Awareness Month".</t>
         </is>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="51" t="n">
         <v>46163</v>
       </c>
       <c r="D8" s="48" t="inlineStr">
@@ -1748,7 +1750,7 @@
           <t>Expressing support for the designation of May 2026 as "Renewable Fuels Month" to recognize the important role that renewable fuels play in lowering fuel prices for consumers, lessening reliance on foreign adversaries, supporting rural communities, and reducing carbon impacts.</t>
         </is>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="51" t="n">
         <v>46163</v>
       </c>
       <c r="D9" s="48" t="inlineStr">
@@ -1785,7 +1787,7 @@
           <t>To require the Transportation Research Board to evaluate innovative hull designs and the use of alternative material construction technologies to enhance operational fleet performance and payload capacity of waterborne transit systems.</t>
         </is>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="51" t="n">
         <v>46163</v>
       </c>
       <c r="D10" s="48" t="inlineStr">
@@ -1822,7 +1824,7 @@
           <t>To amend the Clean Air Act to exclude marginal wells from certain standards of performance and other requirements under such Act, and for other purposes.</t>
         </is>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="51" t="n">
         <v>46163</v>
       </c>
       <c r="D11" s="48" t="inlineStr">
@@ -1859,7 +1861,7 @@
           <t>To realign the nuclear forensics and attribution activities of the Federal Government from the Department of Homeland Security to the National Nuclear Security Administration.</t>
         </is>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="51" t="n">
         <v>46163</v>
       </c>
       <c r="D12" s="48" t="inlineStr">
@@ -1896,7 +1898,7 @@
           <t>To require the Federal Energy Regulatory Commission to establish and maintain the National Utility Rate Change Tracker, and for other purposes.</t>
         </is>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="51" t="n">
         <v>46162</v>
       </c>
       <c r="D13" s="48" t="inlineStr">
@@ -1933,7 +1935,7 @@
           <t>To amend the Public Utility Regulatory Policies Act of 1978 to require States to consider measures that limit the amount of retail utility rate increases an electric utility can request to once every 365 days.</t>
         </is>
       </c>
-      <c r="C14" s="49" t="n">
+      <c r="C14" s="51" t="n">
         <v>46162</v>
       </c>
       <c r="D14" s="48" t="inlineStr">
@@ -1970,7 +1972,7 @@
           <t>To amend the Wild and Scenic Rivers Act to designate the Mullica River watershed in New Jersey for study for potential designation as a wild and scenic river, and for other purposes.</t>
         </is>
       </c>
-      <c r="C15" s="49" t="n">
+      <c r="C15" s="51" t="n">
         <v>46162</v>
       </c>
       <c r="D15" s="48" t="inlineStr">
@@ -2007,7 +2009,7 @@
           <t>Department of Energy Drone Defense Act</t>
         </is>
       </c>
-      <c r="C16" s="49" t="n">
+      <c r="C16" s="51" t="n">
         <v>46162</v>
       </c>
       <c r="D16" s="48" t="inlineStr">
@@ -2044,7 +2046,7 @@
           <t>Designating May 2026 as "National Electrical Safety Month" in the United States and supporting the goals and ideals of "National Electrical Safety Month" to raise awareness of electrical hazards in homes, schools, and workplaces and the action citizens can take to protect against electrically related hazards.</t>
         </is>
       </c>
-      <c r="C17" s="49" t="n">
+      <c r="C17" s="51" t="n">
         <v>46161</v>
       </c>
       <c r="D17" s="48" t="inlineStr">
@@ -19144,7 +19146,7 @@
           <t>A bill to amend the Clean Air Act to exclude marginal wells from certain standards of performance and other requirements under that Act, and for other purposes.</t>
         </is>
       </c>
-      <c r="C6" s="49" t="n">
+      <c r="C6" s="51" t="n">
         <v>46163</v>
       </c>
       <c r="D6" s="48" t="inlineStr">
@@ -19181,7 +19183,7 @@
           <t>A resolution expressing support for the designation of the month of May 2026 as "Progressive Supranuclear Palsy and Corticobasal Degeneration Awareness Month".</t>
         </is>
       </c>
-      <c r="C7" s="49" t="n">
+      <c r="C7" s="51" t="n">
         <v>46163</v>
       </c>
       <c r="D7" s="48" t="inlineStr">
@@ -19218,7 +19220,7 @@
           <t>A resolution expressing support for the designation of May 2026 as "Renewable Fuels Month" to recognize the important role that renewable fuels play in lowering fuel prices for consumers, lessening reliance on foreign adversaries, supporting rural communities, and reducing carbon impacts.</t>
         </is>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="51" t="n">
         <v>46163</v>
       </c>
       <c r="D8" s="48" t="inlineStr">
@@ -19255,7 +19257,7 @@
           <t>A bill to amend the Federal Reserve Act to mandate discount window testing, and for other purposes.</t>
         </is>
       </c>
-      <c r="C9" s="49" t="n">
+      <c r="C9" s="51" t="n">
         <v>46162</v>
       </c>
       <c r="D9" s="48" t="inlineStr">
@@ -19292,7 +19294,7 @@
           <t>A bill to amend the Wild and Scenic Rivers Act to designate the Mullica River watershed in New Jersey for study for potential designation as a wild and scenic river, and for other purposes.</t>
         </is>
       </c>
-      <c r="C10" s="49" t="n">
+      <c r="C10" s="51" t="n">
         <v>46162</v>
       </c>
       <c r="D10" s="48" t="inlineStr">
@@ -19329,7 +19331,7 @@
           <t>A bill to promote the development and use of geothermal resources in the Pacific, and for other purposes.</t>
         </is>
       </c>
-      <c r="C11" s="49" t="n">
+      <c r="C11" s="51" t="n">
         <v>46162</v>
       </c>
       <c r="D11" s="48" t="inlineStr">
@@ -19366,7 +19368,7 @@
           <t>A bill to amend the Geothermal Steam Act of 1970 to provide cost-recovery authority for the Department of the Interior.</t>
         </is>
       </c>
-      <c r="C12" s="49" t="n">
+      <c r="C12" s="51" t="n">
         <v>46162</v>
       </c>
       <c r="D12" s="48" t="inlineStr">
@@ -19403,7 +19405,7 @@
           <t>A bill to require the Environmental Protection Agency to establish a tropospheric ozone research program, and for other purposes.</t>
         </is>
       </c>
-      <c r="C13" s="49" t="n">
+      <c r="C13" s="51" t="n">
         <v>46161</v>
       </c>
       <c r="D13" s="48" t="inlineStr">
